--- a/Data_clean/MCAS/Estados_US/Edos_USA_2022/NEW_HAMPSHIRE_2022.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2022/NEW_HAMPSHIRE_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Chanal</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Ixtapa</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Coquimatlán</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -607,7 +667,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Total</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -669,12 +739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C22">
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -729,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -742,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C27">
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -775,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C29">
@@ -786,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Atlamajalcingo del Monte</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C30">
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -825,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C33">
@@ -838,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -939,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -970,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -983,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -996,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1027,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1047,7 +1212,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C48">
@@ -1058,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C49">
@@ -1071,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -1084,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>San Juan Quiahije</t>
@@ -1097,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>San Juan Quiotepec</t>
@@ -1110,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1141,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C55">
@@ -1154,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1167,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1180,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1200,7 +1410,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C59">
@@ -1211,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1224,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C61">
@@ -1237,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C62">
@@ -1250,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1263,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C64">
@@ -1276,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1307,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1338,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -1351,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1382,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1413,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -1426,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -1439,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C76">
@@ -1452,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -1465,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1496,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1527,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -1540,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1563,41 +1863,6 @@
       </c>
       <c r="D84">
         <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
